--- a/data/ข้อมูลงานตัดหญ้า.xlsx
+++ b/data/ข้อมูลงานตัดหญ้า.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://infracorpth-my.sharepoint.com/personal/inthat_l_infra-corp_co/Documents/rmms/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://infracorpth-my.sharepoint.com/personal/inthat_l_infra-corp_co/Documents/rmms/WL/webapp/workload_webapp/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{2F75D4AE-8D3F-4ED7-A34A-DE61C34C9AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7012E4A-F6ED-42E0-9C4A-4420E257B1A5}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{2F75D4AE-8D3F-4ED7-A34A-DE61C34C9AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5071725F-C411-4AA2-8CD7-CE8B044DDC57}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{36FC6198-A717-441A-9C68-B59D74F0DB1F}"/>
+    <workbookView minimized="1" xWindow="735" yWindow="735" windowWidth="21600" windowHeight="11295" xr2:uid="{36FC6198-A717-441A-9C68-B59D74F0DB1F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -483,13 +483,13 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="group_data_final"/>
+      <sheetName val="ASSET"/>
       <sheetName val="ราคาแผนงานตัดหญ้า"/>
       <sheetName val="แผน68"/>
       <sheetName val="ราคาค่าบำรุง"/>
       <sheetName val="ระยะทาง"/>
       <sheetName val="input"/>
       <sheetName val="ปริมาณน้ำฝน"/>
-      <sheetName val="ASSET"/>
       <sheetName val="ราคาต้นทุน (Asset)"/>
     </sheetNames>
     <sheetDataSet>
